--- a/docs/design-docs/10_プログラム設計書_異常報告・対応指示.xlsx
+++ b/docs/design-docs/10_プログラム設計書_異常報告・対応指示.xlsx
@@ -15,7 +15,875 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="289">
+  <si>
+    <t>版数</t>
+  </si>
+  <si>
+    <t>改訂日</t>
+  </si>
+  <si>
+    <t>改訂内容</t>
+  </si>
+  <si>
+    <t>改訂者</t>
+  </si>
+  <si>
+    <t>承認者</t>
+  </si>
+  <si>
+    <t>区分</t>
+  </si>
+  <si>
+    <t>備考</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>2026/05/23</t>
+  </si>
+  <si>
+    <t>初版作成</t>
+  </si>
+  <si>
+    <t>システム開発部</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>新規</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 異常報告一覧</t>
+  </si>
+  <si>
+    <t>文書管理情報</t>
+  </si>
+  <si>
+    <t>システムID</t>
+  </si>
+  <si>
+    <t>STRUTSLAB-001</t>
+  </si>
+  <si>
+    <t>サブシステム名</t>
+  </si>
+  <si>
+    <t>異常報告</t>
+  </si>
+  <si>
+    <t>プログラムID</t>
+  </si>
+  <si>
+    <t>PG-INC-LIST-001</t>
+  </si>
+  <si>
+    <t>プログラム名</t>
+  </si>
+  <si>
+    <t>異常報告一覧</t>
+  </si>
+  <si>
+    <t>文書番号</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-INC-LIST-001</t>
+  </si>
+  <si>
+    <t>作成日</t>
+  </si>
+  <si>
+    <t>作成者</t>
+  </si>
+  <si>
+    <t>プログラム概要</t>
+  </si>
+  <si>
+    <t>異常報告の複合検索(7条件AND)・一覧。検索条件保存/呼出、一括status更新、CSV/PDF出力。</t>
+  </si>
+  <si>
+    <t>入出力定義</t>
+  </si>
+  <si>
+    <t>項目名</t>
+  </si>
+  <si>
+    <t>型</t>
+  </si>
+  <si>
+    <t>Formプロパティ</t>
+  </si>
+  <si>
+    <t>必須</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>発生日from/to</t>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <t>incDateFrom/To</t>
+  </si>
+  <si>
+    <t>設備種別</t>
+  </si>
+  <si>
+    <t>incEqpType</t>
+  </si>
+  <si>
+    <t>異常種別</t>
+  </si>
+  <si>
+    <t>incType</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>incStatus</t>
+  </si>
+  <si>
+    <t>重大度</t>
+  </si>
+  <si>
+    <t>incSeverity</t>
+  </si>
+  <si>
+    <t>keyword</t>
+  </si>
+  <si>
+    <t>incKeyword</t>
+  </si>
+  <si>
+    <t>部分一致</t>
+  </si>
+  <si>
+    <t>出力</t>
+  </si>
+  <si>
+    <t>検索結果</t>
+  </si>
+  <si>
+    <t>List&amp;lt;IncidentDto&amp;gt;</t>
+  </si>
+  <si>
+    <t>incidentList</t>
+  </si>
+  <si>
+    <t>処理詳細</t>
+  </si>
+  <si>
+    <t>No.</t>
+  </si>
+  <si>
+    <t>処理内容</t>
+  </si>
+  <si>
+    <t>関連DAO</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>検索条件DTO→動的SQL</t>
+  </si>
+  <si>
+    <t>MyBatis &amp;lt;where&amp;gt;&amp;lt;if&amp;gt;</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>DAO.search()(JOIN equipment)</t>
+  </si>
+  <si>
+    <t>IncidentDao</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>検索条件保存:session</t>
+  </si>
+  <si>
+    <t>save/loadCondition</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>一括status更新</t>
+  </si>
+  <si>
+    <t>IncidentDao.bulkUpdateStatus()</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>CSV出力:結果→CSV stream→HttpServletResponse</t>
+  </si>
+  <si>
+    <t>入力検証ルール</t>
+  </si>
+  <si>
+    <t>対象項目</t>
+  </si>
+  <si>
+    <t>検証ルール</t>
+  </si>
+  <si>
+    <t>エラーメッセージ(ja)</t>
+  </si>
+  <si>
+    <t>空可 YYYYMMDD from≦to</t>
+  </si>
+  <si>
+    <t>空可</t>
+  </si>
+  <si>
+    <t>max100</t>
+  </si>
+  <si>
+    <t>状態遷移</t>
+  </si>
+  <si>
+    <t>遷移元</t>
+  </si>
+  <si>
+    <t>遷移先</t>
+  </si>
+  <si>
+    <t>トリガー</t>
+  </si>
+  <si>
+    <t>表示</t>
+  </si>
+  <si>
+    <t>検索結果表示</t>
+  </si>
+  <si>
+    <t>検索</t>
+  </si>
+  <si>
+    <t>条件保存</t>
+  </si>
+  <si>
+    <t>検索条件保存</t>
+  </si>
+  <si>
+    <t>一括更新→再表示</t>
+  </si>
+  <si>
+    <t>実行→confirmOK</t>
+  </si>
+  <si>
+    <t>CSV/PDF</t>
+  </si>
+  <si>
+    <t>struts-config.xml</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>値</t>
+  </si>
+  <si>
+    <t>action path</t>
+  </si>
+  <si>
+    <t>/inc/list</t>
+  </si>
+  <si>
+    <t>action class</t>
+  </si>
+  <si>
+    <t>IncidentListAction</t>
+  </si>
+  <si>
+    <t>form bean</t>
+  </si>
+  <si>
+    <t>IncidentSearchForm</t>
+  </si>
+  <si>
+    <t>scope</t>
+  </si>
+  <si>
+    <t>session</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 異常報告登録</t>
+  </si>
+  <si>
+    <t>PG-INC-CREATE-001</t>
+  </si>
+  <si>
+    <t>異常報告登録</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-INC-CREATE-001</t>
+  </si>
+  <si>
+    <t>異常報告新規登録。点検実施data引継、類似事例検索(同面内表示)、file添付。</t>
+  </si>
+  <si>
+    <t>発生日時</t>
+  </si>
+  <si>
+    <t>incDateTime</t>
+  </si>
+  <si>
+    <t>○</t>
+  </si>
+  <si>
+    <t>引継</t>
+  </si>
+  <si>
+    <t>発見者</t>
+  </si>
+  <si>
+    <t>finder</t>
+  </si>
+  <si>
+    <t>severity</t>
+  </si>
+  <si>
+    <t>異常部位</t>
+  </si>
+  <si>
+    <t>incPart</t>
+  </si>
+  <si>
+    <t>異常詳細</t>
+  </si>
+  <si>
+    <t>incDetail</t>
+  </si>
+  <si>
+    <t>textarea</t>
+  </si>
+  <si>
+    <t>添付file</t>
+  </si>
+  <si>
+    <t>FormFile[]</t>
+  </si>
+  <si>
+    <t>incFiles</t>
+  </si>
+  <si>
+    <t>引継data表示(hidden/session)</t>
+  </si>
+  <si>
+    <t>fromInspection判定</t>
+  </si>
+  <si>
+    <t>類似事例検索:種別+部位→全文→同面下部</t>
+  </si>
+  <si>
+    <t>IncidentDao.searchSimilar()</t>
+  </si>
+  <si>
+    <t>登録:Form→DTO→insert(報告番号INC-YYYYMMDD-NNN)</t>
+  </si>
+  <si>
+    <t>IncidentDao.insert()</t>
+  </si>
+  <si>
+    <t>添付file保存</t>
+  </si>
+  <si>
+    <t>空不可</t>
+  </si>
+  <si>
+    <t>空不可 max2000</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>jpg/png/pdf max10MB</t>
+  </si>
+  <si>
+    <t>類似事例検索→同面下部</t>
+  </si>
+  <si>
+    <t>類似事例検索</t>
+  </si>
+  <si>
+    <t>登録→一覧</t>
+  </si>
+  <si>
+    <t>登録</t>
+  </si>
+  <si>
+    <t>一時保存→表示継続</t>
+  </si>
+  <si>
+    <t>一時保存</t>
+  </si>
+  <si>
+    <t>error→再表示</t>
+  </si>
+  <si>
+    <t>登録→NG</t>
+  </si>
+  <si>
+    <t>/inc/create</t>
+  </si>
+  <si>
+    <t>IncidentCreateAction</t>
+  </si>
+  <si>
+    <t>IncidentForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 異常報告詳細</t>
+  </si>
+  <si>
+    <t>PG-INC-DETAIL-001</t>
+  </si>
+  <si>
+    <t>異常報告詳細</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-INC-DETAIL-001</t>
+  </si>
+  <si>
+    <t>異常報告詳細表示と多段階status遷移。各遷移時条件付必須項目変化。timeline表示。</t>
+  </si>
+  <si>
+    <t>推定原因</t>
+  </si>
+  <si>
+    <t>cause</t>
+  </si>
+  <si>
+    <t>調査中→対応中時○</t>
+  </si>
+  <si>
+    <t>条件付</t>
+  </si>
+  <si>
+    <t>対応内容</t>
+  </si>
+  <si>
+    <t>counterDetail</t>
+  </si>
+  <si>
+    <t>対応中→完了時○</t>
+  </si>
+  <si>
+    <t>異常報告全data</t>
+  </si>
+  <si>
+    <t>IncidentDto</t>
+  </si>
+  <si>
+    <t>incident</t>
+  </si>
+  <si>
+    <t>timeline</t>
+  </si>
+  <si>
+    <t>List&amp;lt;TimelineDto&amp;gt;</t>
+  </si>
+  <si>
+    <t>時系列sort</t>
+  </si>
+  <si>
+    <t>異常報告ID→全data</t>
+  </si>
+  <si>
+    <t>IncidentDao.findById()</t>
+  </si>
+  <si>
+    <t>timeline(時系列sort)</t>
+  </si>
+  <si>
+    <t>IncidentDao.getTimeline()</t>
+  </si>
+  <si>
+    <t>status遷移:現在status→遷移先</t>
+  </si>
+  <si>
+    <t>未了→調査中→対応中→完了→close/CAPA</t>
+  </si>
+  <si>
+    <t>調査→対応:推定原因must</t>
+  </si>
+  <si>
+    <t>Validator+Action内追加</t>
+  </si>
+  <si>
+    <t>対応→完了:対応内容must</t>
+  </si>
+  <si>
+    <t>完了→CAPA:是正処置画面へ</t>
+  </si>
+  <si>
+    <t>Forward:counter.capa</t>
+  </si>
+  <si>
+    <t>調査中→対応中時:空不可</t>
+  </si>
+  <si>
+    <t>対応中→完了時:空不可</t>
+  </si>
+  <si>
+    <t>未了</t>
+  </si>
+  <si>
+    <t>調査中</t>
+  </si>
+  <si>
+    <t>調査開始</t>
+  </si>
+  <si>
+    <t>対応中</t>
+  </si>
+  <si>
+    <t>対応開始(推定原因必須)</t>
+  </si>
+  <si>
+    <t>完了</t>
+  </si>
+  <si>
+    <t>完了(対応内容必須)</t>
+  </si>
+  <si>
+    <t>close</t>
+  </si>
+  <si>
+    <t>是正処置</t>
+  </si>
+  <si>
+    <t>CAPA</t>
+  </si>
+  <si>
+    <t>/inc/detail</t>
+  </si>
+  <si>
+    <t>IncidentDetailAction</t>
+  </si>
+  <si>
+    <t>IncidentForm</t>
+  </si>
+  <si>
+    <t>parameter</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 対応指示登録</t>
+  </si>
+  <si>
+    <t>対応指示</t>
+  </si>
+  <si>
+    <t>PG-CTR-CREATE-001</t>
+  </si>
+  <si>
+    <t>対応指示登録</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-CTR-CREATE-001</t>
+  </si>
+  <si>
+    <t>対応指示新規登録。Header+明細親子構造、Indexed Properties動的行管理、担当者Popup選択。全明細完了check。</t>
+  </si>
+  <si>
+    <t>指示日</t>
+  </si>
+  <si>
+    <t>ctrDate</t>
+  </si>
+  <si>
+    <t>指示者</t>
+  </si>
+  <si>
+    <t>issuer</t>
+  </si>
+  <si>
+    <t>優先度</t>
+  </si>
+  <si>
+    <t>overallPriority</t>
+  </si>
+  <si>
+    <t>明細[{n}].作業内容</t>
+  </si>
+  <si>
+    <t>String[]</t>
+  </si>
+  <si>
+    <t>details[{n}].workContent</t>
+  </si>
+  <si>
+    <t>Indexed</t>
+  </si>
+  <si>
+    <t>明細[{n}].担当者</t>
+  </si>
+  <si>
+    <t>details[{n}].person</t>
+  </si>
+  <si>
+    <t>Popup</t>
+  </si>
+  <si>
+    <t>明細[{n}].期限</t>
+  </si>
+  <si>
+    <t>details[{n}].deadline</t>
+  </si>
+  <si>
+    <t>動的行操作判定(addRow/delRow/save)</t>
+  </si>
+  <si>
+    <t>行追加:配列size+1→INPUT(最下行空行追加)</t>
+  </si>
+  <si>
+    <t>既存行index維持</t>
+  </si>
+  <si>
+    <t>行削除:指定index除去→詰直</t>
+  </si>
+  <si>
+    <t>保存:header+全明細transaction(CTR-YYYYMMDD-NNN)</t>
+  </si>
+  <si>
+    <t>CounterDao</t>
+  </si>
+  <si>
+    <t>全明細完了→header自動完了</t>
+  </si>
+  <si>
+    <t>YYYYMMDD 過去不可</t>
+  </si>
+  <si>
+    <t>詳細行数</t>
+  </si>
+  <si>
+    <t>1行以上 max50</t>
+  </si>
+  <si>
+    <t>行追加→再表示</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>行削除→再表示</t>
+  </si>
+  <si>
+    <t>削除</t>
+  </si>
+  <si>
+    <t>Popup→値反映</t>
+  </si>
+  <si>
+    <t>選択</t>
+  </si>
+  <si>
+    <t>保存→一覧</t>
+  </si>
+  <si>
+    <t>/counter/create</t>
+  </si>
+  <si>
+    <t>CounterCreateAction</t>
+  </si>
+  <si>
+    <t>CounterForm(ValidatorForm)</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 対応指示詳細・完了</t>
+  </si>
+  <si>
+    <t>PG-CTR-DETAIL-001</t>
+  </si>
+  <si>
+    <t>対応指示詳細・完了</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-CTR-DETAIL-001</t>
+  </si>
+  <si>
+    <t>対応指示詳細表示と各明細個別完了報告。完了時実績入力行展開。全明細完了→header自動完了。部品選択→在庫alert。</t>
+  </si>
+  <si>
+    <t>明細[{n}].実績時間</t>
+  </si>
+  <si>
+    <t>actualHours</t>
+  </si>
+  <si>
+    <t>完了時○</t>
+  </si>
+  <si>
+    <t>明細[{n}].使用部品</t>
+  </si>
+  <si>
+    <t>usedPart</t>
+  </si>
+  <si>
+    <t>明細[{n}].使用量</t>
+  </si>
+  <si>
+    <t>Integer[]</t>
+  </si>
+  <si>
+    <t>usedQty</t>
+  </si>
+  <si>
+    <t>明細[{n}].所見</t>
+  </si>
+  <si>
+    <t>note</t>
+  </si>
+  <si>
+    <t>指示ID→全data</t>
+  </si>
+  <si>
+    <t>CounterDao.findById()</t>
+  </si>
+  <si>
+    <t>完了報告展開:指定明細完了form表示</t>
+  </si>
+  <si>
+    <t>INPUT forward</t>
+  </si>
+  <si>
+    <t>明細完了:status=完了 実績保存→在庫引当</t>
+  </si>
+  <si>
+    <t>部品選択→在庫check→発注点下回警告</t>
+  </si>
+  <si>
+    <t>PartsDao.checkStock()</t>
+  </si>
+  <si>
+    <t>警告のみ</t>
+  </si>
+  <si>
+    <t>0より大</t>
+  </si>
+  <si>
+    <t>完了報告展開</t>
+  </si>
+  <si>
+    <t>完了報告</t>
+  </si>
+  <si>
+    <t>展開</t>
+  </si>
+  <si>
+    <t>入力→保存→展開閉</t>
+  </si>
+  <si>
+    <t>保存</t>
+  </si>
+  <si>
+    <t>個別完了</t>
+  </si>
+  <si>
+    <t>最終明細完了時</t>
+  </si>
+  <si>
+    <t>/counter/detail</t>
+  </si>
+  <si>
+    <t>CounterDetailAction</t>
+  </si>
+  <si>
+    <t>CounterDetailForm</t>
+  </si>
+  <si>
+    <t>プログラム設計書 — 是正処置報告書</t>
+  </si>
+  <si>
+    <t>PG-CTR-CAPA-001</t>
+  </si>
+  <si>
+    <t>是正処置報告書</t>
+  </si>
+  <si>
+    <t>DOC-PG-PG-CTR-CAPA-001</t>
+  </si>
+  <si>
+    <t>異常報告派生是正処置報告書登録。なぜなぜ分析5段階、再発防止策、効果確認。</t>
+  </si>
+  <si>
+    <t>なぜ①〜⑤</t>
+  </si>
+  <si>
+    <t>why[1]〜why[5]</t>
+  </si>
+  <si>
+    <t>textarea×5</t>
+  </si>
+  <si>
+    <t>再発防止策</t>
+  </si>
+  <si>
+    <t>countermeasure</t>
+  </si>
+  <si>
+    <t>効果確認方法</t>
+  </si>
+  <si>
+    <t>verifyMethod</t>
+  </si>
+  <si>
+    <t>効果確認期限</t>
+  </si>
+  <si>
+    <t>verifyDate</t>
+  </si>
+  <si>
+    <t>YYYYMMDD 未来日</t>
+  </si>
+  <si>
+    <t>異常報告data→初期表示</t>
+  </si>
+  <si>
+    <t>なぜなぜ:5段階入力→保存</t>
+  </si>
+  <si>
+    <t>再発防止策・効果確認→承認申請</t>
+  </si>
+  <si>
+    <t>CapaDao.insert()</t>
+  </si>
+  <si>
+    <t>why[1]〜[5]</t>
+  </si>
+  <si>
+    <t>空不可 max1000</t>
+  </si>
+  <si>
+    <t>入力→登録→異常報告詳細</t>
+  </si>
+  <si>
+    <t>/counter/capa/create</t>
+  </si>
+  <si>
+    <t>CapaAction</t>
+  </si>
+  <si>
+    <t>CapaForm(ValidatorForm)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
